--- a/public/rider_history.xlsx
+++ b/public/rider_history.xlsx
@@ -69,14 +69,14 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
         <v>1</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -84,7 +84,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -105,14 +105,14 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E3" t="n">
         <v>1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -120,7 +120,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -141,14 +141,14 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E4" t="n">
         <v>1</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -156,7 +156,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -177,14 +177,14 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -192,7 +192,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -213,14 +213,14 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E6" t="n">
         <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -228,7 +228,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -249,14 +249,14 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E7" t="n">
         <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -264,7 +264,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -285,14 +285,14 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E8" t="n">
         <v>1</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -300,7 +300,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -321,14 +321,14 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E9" t="n">
         <v>1</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -336,7 +336,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -357,14 +357,14 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E10" t="n">
         <v>1</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -372,7 +372,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -393,14 +393,14 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E11" t="n">
         <v>1</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -408,7 +408,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -429,14 +429,14 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E12" t="n">
         <v>1</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -444,7 +444,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -465,14 +465,14 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E13" t="n">
         <v>1</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -480,7 +480,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -501,14 +501,14 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E14" t="n">
         <v>1</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -516,7 +516,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -537,14 +537,14 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E15" t="n">
         <v>1</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -573,14 +573,14 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E16" t="n">
         <v>1</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -588,7 +588,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -609,14 +609,14 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E17" t="n">
         <v>1</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -624,7 +624,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -645,14 +645,14 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" t="n">
         <v>1</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -660,7 +660,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -681,14 +681,14 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E19" t="n">
         <v>1</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -717,14 +717,14 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E20" t="n">
         <v>1</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -732,7 +732,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -753,14 +753,14 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E21" t="n">
         <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -768,7 +768,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -789,14 +789,14 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E22" t="n">
         <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -804,7 +804,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -825,14 +825,14 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E23" t="n">
         <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -840,7 +840,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -861,14 +861,14 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E24" t="n">
         <v>1</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -876,7 +876,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -897,14 +897,14 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E25" t="n">
         <v>1</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -912,7 +912,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -933,14 +933,14 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E26" t="n">
         <v>1</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -948,7 +948,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -969,14 +969,14 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E27" t="n">
         <v>1</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -984,7 +984,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1005,14 +1005,14 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" t="n">
         <v>1</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1041,14 +1041,14 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E29" t="n">
         <v>1</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1077,14 +1077,14 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E30" t="n">
         <v>1</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -1092,7 +1092,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1113,14 +1113,14 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E31" t="n">
         <v>1</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -1128,7 +1128,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1149,14 +1149,14 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E32" t="n">
         <v>1</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1185,14 +1185,14 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E33" t="n">
         <v>1</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1221,14 +1221,14 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E34" t="n">
         <v>1</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1257,14 +1257,14 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E35" t="n">
         <v>1</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1293,14 +1293,14 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E36" t="n">
         <v>1</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1329,14 +1329,14 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E37" t="n">
         <v>1</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1365,14 +1365,14 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E38" t="n">
         <v>1</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -1380,7 +1380,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1401,14 +1401,14 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E39" t="n">
         <v>1</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -1416,7 +1416,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1437,14 +1437,14 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E40" t="n">
         <v>1</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1473,14 +1473,14 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E41" t="n">
         <v>1</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -1488,7 +1488,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1509,14 +1509,14 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E42" t="n">
         <v>1</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1545,14 +1545,14 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E43" t="n">
         <v>1</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -1560,7 +1560,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1581,14 +1581,14 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E44" t="n">
         <v>1</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -1596,7 +1596,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1617,14 +1617,14 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E45" t="n">
         <v>1</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1653,14 +1653,14 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E46" t="n">
         <v>1</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1689,14 +1689,14 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" t="n">
         <v>1</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -1704,7 +1704,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1725,14 +1725,14 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" t="n">
         <v>1</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -1761,14 +1761,14 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E49" t="n">
         <v>1</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -1797,14 +1797,14 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E50" t="n">
         <v>1</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -1812,7 +1812,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1833,14 +1833,14 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" t="n">
         <v>1</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -1848,7 +1848,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1869,7 +1869,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1905,7 +1905,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -1920,7 +1920,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -1941,7 +1941,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
@@ -1977,7 +1977,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2013,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
@@ -2028,7 +2028,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
@@ -2064,7 +2064,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2100,7 +2100,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2121,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
@@ -2157,7 +2157,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
@@ -2193,7 +2193,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
@@ -2208,7 +2208,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2229,7 +2229,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
@@ -2244,7 +2244,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2265,7 +2265,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
@@ -2280,7 +2280,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2301,7 +2301,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
@@ -2316,7 +2316,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2337,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
@@ -2352,7 +2352,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2373,7 +2373,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
@@ -2424,7 +2424,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2445,7 +2445,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2481,7 +2481,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
@@ -2532,7 +2532,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2553,7 +2553,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
@@ -2589,7 +2589,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
@@ -2604,7 +2604,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2625,7 +2625,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
@@ -2661,7 +2661,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2697,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
@@ -2733,7 +2733,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
@@ -2769,7 +2769,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2805,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
@@ -2820,7 +2820,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2841,7 +2841,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
@@ -2856,7 +2856,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
@@ -2892,7 +2892,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2913,7 +2913,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -2985,7 +2985,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
@@ -3000,7 +3000,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3021,7 +3021,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
@@ -3036,7 +3036,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3057,7 +3057,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
@@ -3072,7 +3072,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
@@ -3108,7 +3108,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3165,7 +3165,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
@@ -3180,7 +3180,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3201,7 +3201,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
@@ -3216,7 +3216,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3237,7 +3237,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
@@ -3273,7 +3273,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
@@ -3288,7 +3288,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
@@ -3324,7 +3324,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3345,7 +3345,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
@@ -3360,7 +3360,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3381,7 +3381,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
@@ -3453,7 +3453,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3489,7 +3489,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
@@ -3504,7 +3504,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3525,7 +3525,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
@@ -3540,7 +3540,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3561,7 +3561,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
@@ -3597,7 +3597,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
@@ -3633,7 +3633,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
@@ -3648,7 +3648,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3669,7 +3669,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E102" t="n">
         <v>0</v>
@@ -3684,7 +3684,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3705,7 +3705,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E103" t="n">
         <v>0</v>
@@ -3741,7 +3741,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
@@ -3756,7 +3756,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3777,7 +3777,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E105" t="n">
         <v>0</v>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3813,7 +3813,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E106" t="n">
         <v>0</v>
@@ -3828,7 +3828,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3849,7 +3849,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E107" t="n">
         <v>0</v>
@@ -3885,7 +3885,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E108" t="n">
         <v>0</v>
@@ -3900,7 +3900,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3921,7 +3921,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E109" t="n">
         <v>0</v>
@@ -3936,7 +3936,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3957,7 +3957,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E110" t="n">
         <v>0</v>
@@ -3972,7 +3972,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -3993,7 +3993,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E111" t="n">
         <v>0</v>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4029,7 +4029,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E112" t="n">
         <v>0</v>
@@ -4065,7 +4065,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
@@ -4080,7 +4080,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4101,7 +4101,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E114" t="n">
         <v>0</v>
@@ -4137,7 +4137,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E115" t="n">
         <v>0</v>
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E116" t="n">
         <v>0</v>
@@ -4209,7 +4209,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E117" t="n">
         <v>0</v>
@@ -4224,7 +4224,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4245,7 +4245,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4281,7 +4281,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -4296,7 +4296,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4317,7 +4317,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
@@ -4332,7 +4332,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
@@ -4368,7 +4368,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4389,7 +4389,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E122" t="n">
         <v>0</v>
@@ -4404,7 +4404,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4425,7 +4425,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E123" t="n">
         <v>0</v>
@@ -4440,7 +4440,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4461,7 +4461,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E124" t="n">
         <v>0</v>
@@ -4497,7 +4497,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E125" t="n">
         <v>0</v>
@@ -4512,7 +4512,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4533,7 +4533,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E126" t="n">
         <v>0</v>
@@ -4548,7 +4548,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4569,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E127" t="n">
         <v>0</v>
@@ -4584,7 +4584,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E128" t="n">
         <v>0</v>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4641,7 +4641,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E129" t="n">
         <v>0</v>
@@ -4677,7 +4677,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E130" t="n">
         <v>0</v>
@@ -4713,7 +4713,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E131" t="n">
         <v>0</v>
@@ -4728,7 +4728,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4749,7 +4749,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E132" t="n">
         <v>0</v>
@@ -4764,7 +4764,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4785,7 +4785,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E133" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4821,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E134" t="n">
         <v>0</v>
@@ -4836,7 +4836,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4857,7 +4857,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E135" t="n">
         <v>0</v>
@@ -4893,7 +4893,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E136" t="n">
         <v>0</v>
@@ -4908,7 +4908,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E137" t="n">
         <v>0</v>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4965,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E138" t="n">
         <v>0</v>
@@ -4980,7 +4980,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E139" t="n">
         <v>0</v>
@@ -5037,7 +5037,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E140" t="n">
         <v>0</v>
@@ -5052,7 +5052,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5073,7 +5073,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E141" t="n">
         <v>0</v>
@@ -5088,7 +5088,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E142" t="n">
         <v>0</v>
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5145,7 +5145,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E143" t="n">
         <v>0</v>
@@ -5181,7 +5181,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E144" t="n">
         <v>0</v>
@@ -5217,7 +5217,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E145" t="n">
         <v>0</v>
@@ -5232,7 +5232,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5253,7 +5253,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E146" t="n">
         <v>0</v>
@@ -5289,7 +5289,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E147" t="n">
         <v>0</v>
@@ -5304,7 +5304,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5325,7 +5325,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E148" t="n">
         <v>0</v>
@@ -5361,7 +5361,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E149" t="n">
         <v>0</v>
@@ -5397,7 +5397,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E150" t="n">
         <v>0</v>
@@ -5433,7 +5433,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E151" t="n">
         <v>0</v>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5469,7 +5469,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E152" t="n">
         <v>0</v>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5505,7 +5505,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E153" t="n">
         <v>0</v>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5541,7 +5541,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E154" t="n">
         <v>0</v>
@@ -5556,7 +5556,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5577,7 +5577,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E155" t="n">
         <v>0</v>
@@ -5592,7 +5592,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5613,7 +5613,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E156" t="n">
         <v>0</v>
@@ -5649,7 +5649,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E157" t="n">
         <v>0</v>
@@ -5685,7 +5685,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E158" t="n">
         <v>0</v>
@@ -5721,7 +5721,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E159" t="n">
         <v>0</v>
@@ -5736,7 +5736,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5757,7 +5757,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E160" t="n">
         <v>0</v>
@@ -5772,7 +5772,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5793,7 +5793,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E161" t="n">
         <v>0</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E162" t="n">
         <v>0</v>
@@ -5844,7 +5844,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5865,7 +5865,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E163" t="n">
         <v>0</v>
@@ -5880,7 +5880,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E164" t="n">
         <v>0</v>
@@ -5916,7 +5916,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5937,7 +5937,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E165" t="n">
         <v>0</v>
@@ -5952,7 +5952,7 @@
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -5973,7 +5973,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E166" t="n">
         <v>0</v>
@@ -6009,7 +6009,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E167" t="n">
         <v>0</v>
@@ -6045,7 +6045,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E168" t="n">
         <v>0</v>
@@ -6060,7 +6060,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E169" t="n">
         <v>0</v>
@@ -6096,7 +6096,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6117,7 +6117,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E170" t="n">
         <v>0</v>
@@ -6132,7 +6132,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6153,7 +6153,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E171" t="n">
         <v>0</v>
@@ -6168,7 +6168,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6189,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E172" t="n">
         <v>0</v>
@@ -6204,7 +6204,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6225,7 +6225,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E173" t="n">
         <v>0</v>
@@ -6240,7 +6240,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6261,7 +6261,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E174" t="n">
         <v>0</v>
@@ -6276,7 +6276,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E175" t="n">
         <v>0</v>
@@ -6312,7 +6312,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E176" t="n">
         <v>0</v>
@@ -6348,7 +6348,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6369,7 +6369,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E177" t="n">
         <v>0</v>
@@ -6405,7 +6405,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E178" t="n">
         <v>0</v>
@@ -6441,7 +6441,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E179" t="n">
         <v>0</v>
@@ -6456,7 +6456,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6477,7 +6477,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E180" t="n">
         <v>0</v>
@@ -6492,7 +6492,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E181" t="n">
         <v>0</v>
@@ -6549,7 +6549,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E182" t="n">
         <v>0</v>
@@ -6564,7 +6564,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6585,7 +6585,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E183" t="n">
         <v>0</v>
@@ -6600,7 +6600,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6621,7 +6621,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E184" t="n">
         <v>0</v>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6657,7 +6657,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E185" t="n">
         <v>0</v>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6693,7 +6693,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E186" t="n">
         <v>0</v>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E187" t="n">
         <v>0</v>
@@ -6744,7 +6744,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6765,7 +6765,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E188" t="n">
         <v>0</v>
@@ -6780,7 +6780,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6801,7 +6801,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E189" t="n">
         <v>0</v>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6837,7 +6837,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E190" t="n">
         <v>0</v>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6873,7 +6873,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E191" t="n">
         <v>0</v>
@@ -6888,7 +6888,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6909,7 +6909,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E192" t="n">
         <v>0</v>
@@ -6945,7 +6945,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E193" t="n">
         <v>0</v>
@@ -6960,7 +6960,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -6981,7 +6981,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E194" t="n">
         <v>0</v>
@@ -7017,7 +7017,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E195" t="n">
         <v>0</v>
@@ -7032,7 +7032,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7053,7 +7053,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E196" t="n">
         <v>0</v>
@@ -7068,7 +7068,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7089,7 +7089,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E197" t="n">
         <v>0</v>
@@ -7125,7 +7125,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E198" t="n">
         <v>0</v>
@@ -7140,7 +7140,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7161,7 +7161,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E199" t="n">
         <v>0</v>
@@ -7197,7 +7197,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E200" t="n">
         <v>0</v>
@@ -7233,7 +7233,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E201" t="n">
         <v>0</v>
@@ -7248,7 +7248,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7269,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E202" t="n">
         <v>0</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E203" t="n">
         <v>0</v>
@@ -7320,7 +7320,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E204" t="n">
         <v>0</v>
@@ -7356,7 +7356,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7377,7 +7377,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E205" t="n">
         <v>0</v>
@@ -7413,7 +7413,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E206" t="n">
         <v>0</v>
@@ -7428,7 +7428,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E207" t="n">
         <v>0</v>
@@ -7485,7 +7485,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E208" t="n">
         <v>0</v>
@@ -7500,7 +7500,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7521,7 +7521,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E209" t="n">
         <v>0</v>
@@ -7536,7 +7536,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E210" t="n">
         <v>0</v>
@@ -7572,7 +7572,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7593,7 +7593,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E211" t="n">
         <v>0</v>
@@ -7629,7 +7629,7 @@
         </is>
       </c>
       <c r="D212" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E212" t="n">
         <v>0</v>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7665,7 +7665,7 @@
         </is>
       </c>
       <c r="D213" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E213" t="n">
         <v>0</v>
@@ -7680,7 +7680,7 @@
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
         </is>
       </c>
       <c r="D214" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E214" t="n">
         <v>0</v>
@@ -7716,7 +7716,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7737,7 +7737,7 @@
         </is>
       </c>
       <c r="D215" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E215" t="n">
         <v>0</v>
@@ -7752,7 +7752,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7773,7 +7773,7 @@
         </is>
       </c>
       <c r="D216" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E216" t="n">
         <v>0</v>
@@ -7809,7 +7809,7 @@
         </is>
       </c>
       <c r="D217" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E217" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
         </is>
       </c>
       <c r="D218" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E218" t="n">
         <v>0</v>
@@ -7860,7 +7860,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7881,7 +7881,7 @@
         </is>
       </c>
       <c r="D219" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E219" t="n">
         <v>0</v>
@@ -7917,7 +7917,7 @@
         </is>
       </c>
       <c r="D220" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E220" t="n">
         <v>0</v>
@@ -7953,7 +7953,7 @@
         </is>
       </c>
       <c r="D221" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E221" t="n">
         <v>0</v>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -7989,7 +7989,7 @@
         </is>
       </c>
       <c r="D222" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E222" t="n">
         <v>0</v>
@@ -8004,7 +8004,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8025,7 +8025,7 @@
         </is>
       </c>
       <c r="D223" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E223" t="n">
         <v>0</v>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8061,7 +8061,7 @@
         </is>
       </c>
       <c r="D224" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E224" t="n">
         <v>0</v>
@@ -8097,7 +8097,7 @@
         </is>
       </c>
       <c r="D225" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E225" t="n">
         <v>0</v>
@@ -8133,7 +8133,7 @@
         </is>
       </c>
       <c r="D226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E226" t="n">
         <v>0</v>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8169,7 +8169,7 @@
         </is>
       </c>
       <c r="D227" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E227" t="n">
         <v>0</v>
@@ -8184,7 +8184,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
         </is>
       </c>
       <c r="D228" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E228" t="n">
         <v>0</v>
@@ -8220,7 +8220,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8241,7 +8241,7 @@
         </is>
       </c>
       <c r="D229" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E229" t="n">
         <v>0</v>
@@ -8256,7 +8256,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8277,7 +8277,7 @@
         </is>
       </c>
       <c r="D230" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E230" t="n">
         <v>0</v>
@@ -8313,7 +8313,7 @@
         </is>
       </c>
       <c r="D231" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E231" t="n">
         <v>0</v>
@@ -8328,7 +8328,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8349,7 +8349,7 @@
         </is>
       </c>
       <c r="D232" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E232" t="n">
         <v>0</v>
@@ -8364,7 +8364,7 @@
       </c>
       <c r="H232" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8385,7 +8385,7 @@
         </is>
       </c>
       <c r="D233" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E233" t="n">
         <v>0</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="D234" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E234" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8457,7 +8457,7 @@
         </is>
       </c>
       <c r="D235" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E235" t="n">
         <v>0</v>
@@ -8472,7 +8472,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8493,7 +8493,7 @@
         </is>
       </c>
       <c r="D236" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E236" t="n">
         <v>0</v>
@@ -8508,7 +8508,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8529,7 +8529,7 @@
         </is>
       </c>
       <c r="D237" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E237" t="n">
         <v>0</v>
@@ -8565,7 +8565,7 @@
         </is>
       </c>
       <c r="D238" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E238" t="n">
         <v>0</v>
@@ -8580,7 +8580,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8601,7 +8601,7 @@
         </is>
       </c>
       <c r="D239" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E239" t="n">
         <v>0</v>
@@ -8616,7 +8616,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8637,7 +8637,7 @@
         </is>
       </c>
       <c r="D240" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E240" t="n">
         <v>0</v>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8673,7 +8673,7 @@
         </is>
       </c>
       <c r="D241" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E241" t="n">
         <v>0</v>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8709,7 +8709,7 @@
         </is>
       </c>
       <c r="D242" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E242" t="n">
         <v>0</v>
@@ -8745,7 +8745,7 @@
         </is>
       </c>
       <c r="D243" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E243" t="n">
         <v>0</v>
@@ -8760,7 +8760,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="D244" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E244" t="n">
         <v>0</v>
@@ -8796,7 +8796,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8817,7 +8817,7 @@
         </is>
       </c>
       <c r="D245" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E245" t="n">
         <v>0</v>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8853,7 +8853,7 @@
         </is>
       </c>
       <c r="D246" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E246" t="n">
         <v>0</v>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8889,7 +8889,7 @@
         </is>
       </c>
       <c r="D247" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E247" t="n">
         <v>0</v>
@@ -8904,7 +8904,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8925,7 +8925,7 @@
         </is>
       </c>
       <c r="D248" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E248" t="n">
         <v>0</v>
@@ -8940,7 +8940,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
     </row>
@@ -8961,7 +8961,7 @@
         </is>
       </c>
       <c r="D249" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E249" t="n">
         <v>0</v>
